--- a/sharedata/excel/Z-装备强化表(EquipStrData).xlsx
+++ b/sharedata/excel/Z-装备强化表(EquipStrData).xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\策划文档\配置表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ThroneOfAshes_Client\sharedata\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,13 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
-  <si>
-    <t>品质映射使用公共品质表；普通、优良不强化，相关配置留空；精锐及以上可强化。</t>
-  </si>
-  <si>
-    <t>强化上限、主属性加成和各级所需经验待配置；need_exp用//分隔，长度须等于max_level。</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>装备强化表</t>
   </si>
@@ -109,16 +103,31 @@
     <t>蓝</t>
   </si>
   <si>
+    <t>80//200//360//560//800//1080</t>
+  </si>
+  <si>
     <t>紫</t>
   </si>
   <si>
+    <t>140//350//630//980//1400//1890//2450//3080//3780</t>
+  </si>
+  <si>
     <t>金</t>
   </si>
   <si>
+    <t>260//650//1170//1820//2600//3510//4550//5720//7020//8450//10010//11700</t>
+  </si>
+  <si>
     <t>红</t>
   </si>
   <si>
+    <t>600//1500//2700//4200//6000//8100//10500//13200//16200//19500//23100//27000//31200//35700//40500</t>
+  </si>
+  <si>
     <t>彩</t>
+  </si>
+  <si>
+    <t>1200//3000//5400//8400//12000//16200//21000//26400//32400//39000//46200//54000//62400//71400//81000//91200//102000//113400//125400//138000</t>
   </si>
 </sst>
 </file>
@@ -131,7 +140,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -174,6 +183,13 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -188,13 +204,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFE58FBC"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -349,13 +358,6 @@
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-      <b/>
-      <color rgb="FFFF0000"/>
     </font>
   </fonts>
   <fills count="34">
@@ -830,7 +832,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -838,12 +840,18 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -853,23 +861,20 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1345,226 +1350,219 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="13.2083333333333" customWidth="1"/>
-    <col min="2" max="2" width="9.38333333333333" customWidth="1"/>
-    <col min="3" max="3" width="20.0833333333333" customWidth="1"/>
-    <col min="4" max="4" width="12.75" customWidth="1"/>
-    <col min="5" max="5" width="14.5833333333333" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
+    <col min="1" max="1" width="13.625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="5.625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.25" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="15" style="3" customWidth="1"/>
+    <col min="6" max="6" width="36.375" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="16.5" spans="1:6">
+      <c r="A1" s="5"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" ht="16.5" spans="1:6">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="15" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" spans="1:6">
-      <c r="A2" s="3" t="s">
+    <row r="4" s="2" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:6">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="C7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
     </row>
-    <row r="3" s="1" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
-      <c r="A3" s="1" t="s">
+    <row r="8" ht="16.5" spans="1:6">
+      <c r="A8" s="5"/>
+      <c r="B8" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="C8" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" ht="16.5" spans="1:6">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5">
         <v>3</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="5">
+        <v>6</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:6">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5">
         <v>4</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="C10" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="5">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:6">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="C11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="5">
+        <v>12</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:6">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5">
         <v>6</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="C12" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="5">
+        <v>15</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:6">
+      <c r="A13" s="5"/>
+      <c r="B13" s="5">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="C13" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="5">
         <v>20</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" customHeight="1" spans="1:6">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4">
-        <v>1</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="4">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" ht="16.5" customHeight="1" spans="1:6">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4">
-        <v>2</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" ht="16.5" customHeight="1" spans="1:6">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4">
-        <v>3</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="4">
-        <v>6</v>
-      </c>
-      <c r="E9" s="4">
+      <c r="E13" s="5">
         <v>0.2</v>
       </c>
-      <c r="F9" s="12" t="str">
-        <v>80//200//360//560//800//1080</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" customHeight="1" spans="1:6">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4">
-        <v>4</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="4">
-        <v>9</v>
-      </c>
-      <c r="E10" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="F10" s="12" t="str">
-        <v>140//350//630//980//1400//1890//2450//3080//3780</v>
-      </c>
-    </row>
-    <row r="11" ht="33.0" customHeight="1" spans="1:6">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4">
-        <v>5</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="4">
-        <v>12</v>
-      </c>
-      <c r="E11" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="F11" s="13" t="str">
-        <v>260//650//1170//1820//2600//3510//4550//5720//7020//8450//10010//11700</v>
-      </c>
-    </row>
-    <row r="12" ht="49.5" customHeight="1" spans="1:6">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4">
-        <v>6</v>
-      </c>
-      <c r="C12" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="4">
-        <v>15</v>
-      </c>
-      <c r="E12" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="F12" s="13" t="str">
-        <v>600//1500//2700//4200//6000//8100//10500//13200//16200//19500//23100//27000//31200//35700//40500</v>
-      </c>
-    </row>
-    <row r="13" ht="49.5" customHeight="1" spans="1:6">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4">
-        <v>7</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="4">
-        <v>20</v>
-      </c>
-      <c r="E13" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="F13" s="13" t="str">
-        <v>1200//3000//5400//8400//12000//16200//21000//26400//32400//39000//46200//54000//62400//71400//81000//91200//102000//113400//125400//138000</v>
+      <c r="F13" s="10" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
